--- a/xlsx/AC-C.xlsx
+++ b/xlsx/AC-C.xlsx
@@ -749,12 +749,12 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>벽 지지형 천장 · 마감판 상향</t>
+          <t>벽 지지형 천장 · 기존 천장 질량 보강</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>유닛 123 + 공동</t>
+          <t>유닛 119 + 공동</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>질량의 절벽 — 구조 동일, 돌차음판 4T만 추가. 100Hz 이하 대응 여부가 갈림. @450 표준</t>
+          <t>질량의 절벽 — 유닛 동일, 기존 천장 하면에 돌차음판 4T 덧붙임. 100Hz 이하 대응 여부가 갈림. 스팬 · 하중 불변</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr"/>
@@ -1206,7 +1206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D99"/>
+  <dimension ref="A1:D83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1225,14 +1225,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>벽 지지형 천장 · 마감판 상향</t>
+          <t>벽 지지형 천장 · 기존 천장 질량 보강</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>Wall-borne ceiling / mass loaded</t>
+          <t>Wall-borne ceiling / existing ceiling mass loaded</t>
         </is>
       </c>
     </row>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>유닛 123 + 공동</t>
+          <t>유닛 119 + 공동</t>
         </is>
       </c>
     </row>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>AC-00 · AC-R</t>
+          <t>AC-00 · AC-W-M2</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -1336,31 +1336,31 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>벽 지지형 천장 · 마감판 상향</t>
+          <t>벽 지지형 천장 · 기존 천장 질량 보강</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>지지</t>
+          <t>구조</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>벽 유닛 상단 턱 — 슬래브 접촉 0</t>
+          <t>M1과 완전 동일 — 유닛 · 지지 · 공동 · 보 사양 불변</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>슬래브 타공</t>
+          <t>M2 진입점</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>없음 · 원상복구 가능</t>
+          <t>기존 천장 하면에 돌차음판 4T 덧붙임</t>
         </is>
       </c>
     </row>
@@ -1372,946 +1372,776 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>전면 존치 (목상 + 석고 9.5 + 벽지)</t>
+          <t>전면 존치 + 돌차음판 4T 부착 (철거 없음 · 원상복구 가능)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>새 공동</t>
+          <t>삼중 리프 질량</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>200 mm 이상 · 유닛 상면 마블로 충진</t>
+          <t>슬래브 460 / 기존 천장 7.2 → 13.7 / 유닛 19 (kg/㎡)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>보</t>
+          <t>유닛 구조층</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>박스빔 — 다루끼 28×67 + 합판 3~5T 양면</t>
+          <t>마블 50 + PB 15 + 마블 50 = 115 mm — M1 동일</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>보 간격</t>
+          <t>천장 자중</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>@450 표준 — 스팬 2.7m / @600 — 스팬 2.4m</t>
+          <t>약 19 kg/㎡ — M1 동일</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>유닛 구조층</t>
+          <t>보 간격</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>마블 50 + PB 15 + 돌차음판 4 + 마블 50 = 119 mm</t>
+          <t>@600 — 스팬 2.7m / @450 — 스팬 2.9m — M1 동일</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>구조</t>
+          <t>벽 하단 응력</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>M1과 완전 동일 — 지지 · 공동 · 보 사양 불변</t>
+          <t>분산판 적용 시 약 3.5 kPa — M1 동일</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>유닛 상면</t>
+          <t>기존 달대 추가 하중</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>마블 50T 사전 접착 — 새 공동 충진</t>
+          <t>약 6.5 kg/㎡ — 기존 석고 7.2 → 13.7</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>마감</t>
+          <t>대응</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>흡음텍스 · 벽 안쪽 면까지 (구조 무관)</t>
+          <t>M1 + 100Hz 대역 보완</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>천장 자중</t>
+          <t>비대응</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>약 25.5 kg/㎡ (흡음텍스 제외)</t>
+          <t>위층 뛰는 소리 · 대출력 저역</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>스팬 한계</t>
+          <t>적용</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>@450 2.7m / @600 2.4m · 초과 시 짧은 변 방향</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>벽 하단 응력</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>분산판 적용 시 약 3.7 kPa</t>
+          <t>피아노 · 첼로 · 콘트라베이스 · 튜바 · 앰프 · 모니터 스피커 (100Hz 이하)</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>대응</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>M1 + 100Hz 대역 보완 · 전 대역 약 4dB 상승</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>비대응</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>위층 뛰는 소리 · 대출력 저역</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t>어쿠스틱 드럼</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>불가 — 부유바닥 필요 · 아파트 바닥고 부족</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="9" t="inlineStr">
-        <is>
-          <t>적용</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>피아노 · 첼로 · 콘트라베이스 · 튜바 · 앰프 · 모니터 스피커 (100Hz 이하)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>설계 근거</t>
         </is>
       </c>
-      <c r="B33" s="4" t="n"/>
-      <c r="C33" s="4" t="n"/>
-      <c r="D33" s="4" t="n"/>
-    </row>
-    <row r="34" ht="56" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>M1과 구조가 완전히 동일하다. 지지 · 공동 · 보 사양을 그대로 두고 유닛 안에 돌차음판 4T만 삽입한다. 남은 변수가 질량뿐이므로 구조에 차이를 두지 않는다. 슬래브 무접촉인 점도 M1과 같다 —  M1은 벽 유닛 상단 턱에 얹혀 접촉점이 0이다. 6면이 하나의 계로 묶여 사실상 박스인박스에 가까워진다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="56" customHeight="1">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>합판 웨브가 3~5T로 얇은 이유는 강성이 아니다. 국산 각재의 뒤틀림 방지, 유닛이 끼워지는 가이드 면, 28mm 폭 각재의 전도 방지가 목적이다. 두껍게 해도 강성은 거의 늘지 않고 무게와 비용만 올라가므로 얇게 대는 것이 합리적이다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="56" customHeight="1">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>보 춤 67mm와 유닛 두께의 정합 — 다루끼 28×67의 춤이 유닛 구조층과 맞물리도록 설계한다. 유닛이 보 사이에 끼워지므로 보 하부 받침 턱 유무를 제작 전 확인한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="56" customHeight="1">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t>유닛 상면 마블은 선택이 아니라 표준이다. 유닛 구성만으로는 슬래브~유닛 사이 200mm 공동이 완전히 비어 정재파가 선다. 상면에 마블 50T를 사전 접착하면 자중은 약 2kg/㎡만 늘고 머리 위 작업도 없다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="56" customHeight="1">
-      <c r="A42" s="7" t="inlineStr">
-        <is>
-          <t>PB가 위, 마블이 아래인 이유 — 천장은 중력 방향이 벽과 반대라 마블이 아래로 처진다. 흡음텍스가 받쳐주는 구조이며, 보 하부 받침 턱으로 이중 확보한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="56" customHeight="1">
-      <c r="A44" s="7" t="inlineStr">
-        <is>
-          <t>흡음텍스는 구조가 아니다. 하중은 마블 50 하단까지가 지지선이며 텍스는 벽 안쪽 면까지만 들어온다. 벽 마감과 만나는 지점은 5~10mm 그림자 홈으로 처리해 장기 처짐을 흡수한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="56" customHeight="1">
-      <c r="A46" s="7" t="inlineStr">
-        <is>
-          <t>삼중 리프는 제거할 수 없다. 슬래브 460 · 기존 석고 7.2 · 유닛 10.2의 세 판이 성립하며, 아래 두 판의 질량이 가까워 두 공진이 겹친다. 실내측 판을 무겁게 하면 벌어지지만 자중과 스팬 대가가 크므로 마지막 카드로 둔다.</t>
+      <c r="B28" s="4" t="n"/>
+      <c r="C28" s="4" t="n"/>
+      <c r="D28" s="4" t="n"/>
+    </row>
+    <row r="29" ht="56" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>질량을 유닛이 아니라 기존 천장에 더한다. 삼중 리프의 약점은 가운데 판(기존 석고 7.2)이 너무 가볍다는 것이다. 실내측 유닛을 무겁게 해 벌리는 대신 가운데 판에 직접 돌차음판 4T를 붙이면 7.2 → 13.7이 되어 두 공진이 벌어진다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="56" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>유닛은 M1과 완전히 같다. 돌차음판이 기존 달대에 매달리므로 벽 위 하중 · 보 스팬 · 벽 하단 응력이 M1과 동일하다. @600 유지, 3.5kPa 유지. M1 → M2 업그레이드가 유닛 재제작 없이 성립한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="56" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>철거가 아니라 덧붙임이다. 기존 석고 하면에 자체 점착으로 부착하므로 원상복구 조건에 걸리지 않는다. 퇴거 시 돌차음판을 떼어내거나 그 위에 벽지를 재시공한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="56" customHeight="1">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>기존 달대 하중을 확인한다. 경량 천장 기준 달대에 기존 석고 7.2 + 돌차음판 6.5 = 13.7kg/㎡가 걸린다. 약 두 배이므로 노후 세대는 달대 이완 · 부식 여부를 먼저 본다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="56" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>머리 위 작업이 생긴다. 유닛 사전 접착과 달리 현장 부착이다. 다만 1000×1000 한 장 6.5kg으로 1인 작업이 가능하고, 유닛 거치 전에 하므로 작업 공간이 확보된다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>자재</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="n"/>
+      <c r="C39" s="4" t="n"/>
+      <c r="D39" s="4" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>규격</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>돌차음판</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>4T · 자체 점착</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>기존 천장 하면 — M2 진입점</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>박스빔 각재</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>다루끼 28×67</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>M1 동일</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>박스빔 합판</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>3~5T 양면</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>M1 동일</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>유닛 상면 마블</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>50T</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>사전 접착 · 공동 충진</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>PB</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>15T</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>유닛 구조판</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>마블</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>50T</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>유닛 하부</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>흡음텍스</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>지정</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>마감</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>자재</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="n"/>
-      <c r="C48" s="4" t="n"/>
-      <c r="D48" s="4" t="n"/>
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>벽 상단 턱</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>각재 권장</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>M1 동일</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>구분</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="inlineStr">
-        <is>
-          <t>규격</t>
-        </is>
-      </c>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>비고</t>
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>하중분산판</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>합판 18T</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>M1 동일</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>박스빔 각재</t>
+          <t>탄성 실란트</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>다루끼 28×67</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>웨브</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>박스빔 합판</t>
-        </is>
-      </c>
-      <c r="B51" s="6" t="inlineStr">
-        <is>
-          <t>3~5T 양면</t>
-        </is>
-      </c>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
-          <t>뒤틀림 방지 · 가이드 면</t>
+          <t>벽 접합부 그림자 홈</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>유닛 상면 마블</t>
-        </is>
-      </c>
-      <c r="B52" s="6" t="inlineStr">
-        <is>
-          <t>50T</t>
-        </is>
-      </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t>사전 접착 · 새 공동 충진</t>
-        </is>
-      </c>
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>시공 순서</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="n"/>
+      <c r="C52" s="4" t="n"/>
+      <c r="D52" s="4" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>PB</t>
-        </is>
-      </c>
-      <c r="B53" s="6" t="inlineStr">
-        <is>
-          <t>15T</t>
-        </is>
-      </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t>유닛 구조판</t>
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>작업</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>확인사항</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>돌차음판</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>4T · 자체 점착</t>
+          <t>기존 천장 존치 확인</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>PB 아래 · 지상 사전 접착 — M2 진입점</t>
+          <t>철거하지 않음</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>마블</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>50T</t>
+          <t>기존 달대 · 목상 상태 확인</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>유닛 하부 · 실내측 흡음 배후층</t>
+          <t>이완 · 부식 · 처짐 — 추가 하중 6.5kg/㎡ 검토</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>흡음텍스</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>지정</t>
+          <t>기존 천장 하면 정리</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>마감 · 구조 무관</t>
+          <t>벽지 상태 확인 · 들뜸 재고정</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>벽 상단 턱</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>각재 권장</t>
+          <t>돌차음판 4T 부착</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>PB일 경우 각재 보강</t>
+          <t>기존 천장 하면 · 이형지 20~30cm씩 · 이음부 밀착</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>하중분산판</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>합판 18T · 접지 폭 300</t>
+          <t>방 폭 실측 · 스팬 판정</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>벽 하단 · AC-F 참조</t>
+          <t>M1 동일</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>차음석고보드</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>12.5T</t>
+          <t>벽 유닛 · 분산판 · 방진층</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>성능 보강 시 · 하중 재검토 전제</t>
+          <t>M1 동일</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>탄성 실란트</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>박스빔 제작 · 거치</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>벽 접합부 그림자 홈</t>
+          <t>M1 동일 · 돌차음판과 비접촉 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>천장 유닛 제작 · 거치</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>M1 동일 · 상면 마블 사전 접착</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="inlineStr">
-        <is>
-          <t>시공 순서</t>
-        </is>
-      </c>
-      <c r="B62" s="4" t="n"/>
-      <c r="C62" s="4" t="n"/>
-      <c r="D62" s="4" t="n"/>
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>슬래브 · 돌차음판 비접촉 최종 확인</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>유닛 상면 마블이 돌차음판에 닿지 않도록</t>
+        </is>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>작업</t>
-        </is>
-      </c>
-      <c r="C63" s="5" t="inlineStr">
-        <is>
-          <t>확인사항</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B64" s="6" t="inlineStr">
-        <is>
-          <t>기존 천장 존치 확인</t>
-        </is>
-      </c>
-      <c r="C64" s="6" t="inlineStr">
-        <is>
-          <t>철거하지 않음 · 원상복구 조건</t>
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>흡음텍스 마감</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>M1 동일</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B65" s="6" t="inlineStr">
-        <is>
-          <t>방 폭 실측 · 스팬 판정</t>
-        </is>
-      </c>
-      <c r="C65" s="6" t="inlineStr">
-        <is>
-          <t>2.7m 이하 @600 / 초과 시 @450</t>
-        </is>
-      </c>
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>시공상 유의사항</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="n"/>
+      <c r="C65" s="4" t="n"/>
+      <c r="D65" s="4" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B66" s="6" t="inlineStr">
-        <is>
-          <t>벽 유닛 시공 · 상단 턱 확인</t>
-        </is>
-      </c>
-      <c r="C66" s="6" t="inlineStr">
-        <is>
-          <t>턱 재료 · 지압면 폭</t>
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>내용</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>기존 달대 하중</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>벽 하단 분산판 · 방진층</t>
-        </is>
-      </c>
-      <c r="C67" s="6" t="inlineStr">
-        <is>
-          <t>AC-F 방진층 위 · 접지 폭 300</t>
+          <t>기존 석고 7.2에 돌차음판 6.5가 더해져 약 두 배가 된다. 노후 세대는 달대 이완 · 부식을 확인하고 필요 시 보강한다.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>돌차음판 · 유닛 비접촉</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>박스빔 제작</t>
-        </is>
-      </c>
-      <c r="C68" s="6" t="inlineStr">
-        <is>
-          <t>다루끼 + 합판 3~5T 양면</t>
+          <t>새 공동이 줄어들므로 유닛 상면 마블이 돌차음판에 닿지 않는지 확인한다. 닿으면 가운데 판과 유닛이 연결되어 삼중 리프 분리 효과가 사라진다.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>부착면 상태</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>박스빔 거치</t>
-        </is>
-      </c>
-      <c r="C69" s="6" t="inlineStr">
-        <is>
-          <t>벽 상단 턱에 양단 지지 · 슬래브 비접촉 확인</t>
+          <t>벽지 위에 붙이면 벽지가 떨어지며 돌차음판이 처질 수 있다. 벽지 들뜸을 확인하고, 불량 구간은 벽지를 제거한 뒤 석고면에 직접 붙인다.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>이음부 처리</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>천장 유닛 제작</t>
-        </is>
-      </c>
-      <c r="C70" s="6" t="inlineStr">
-        <is>
-          <t>상면 마블 50 + 돌차음판 4T 사전 접착</t>
+          <t>돌차음판 이음부에 틈이 생기면 그 자리가 질량 결손이 된다. 밀착 후 테이핑한다.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>원상복구 고지</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>유닛 거치</t>
-        </is>
-      </c>
-      <c r="C71" s="6" t="inlineStr">
-        <is>
-          <t>보 사이 끼움 · 하부 받침 턱 확인</t>
+          <t>퇴거 시 돌차음판을 제거하거나 그 위에 벽지를 재시공한다. 계약 시 처리 방법을 명시한다.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>성능 범위 고지</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>유닛 간 이음부 처리</t>
-        </is>
-      </c>
-      <c r="C72" s="6" t="inlineStr">
-        <is>
-          <t>공극 없이 밀착</t>
+          <t>위층 뛰는 소리와 대출력 저역은 대응하지 않는다. 100Hz 딥은 완화되지만 삼중 리프 자체는 남는다.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>M1과의 차이</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>슬래브 비접촉 최종 확인</t>
-        </is>
-      </c>
-      <c r="C73" s="6" t="inlineStr">
-        <is>
-          <t>배관 · 배선 · 유닛 상면 전부</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="6" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B74" s="6" t="inlineStr">
-        <is>
-          <t>흡음텍스 마감</t>
-        </is>
-      </c>
-      <c r="C74" s="6" t="inlineStr">
-        <is>
-          <t>벽 안쪽 면까지 · 그림자 홈 5~10mm</t>
-        </is>
-      </c>
+          <t>견적 차이는 돌차음판 자재비와 부착 공수뿐이다. 유닛 · 보 · 벽 하단은 M1과 동일하다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>금지사항</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="n"/>
+      <c r="C75" s="4" t="n"/>
+      <c r="D75" s="4" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="3" t="inlineStr">
-        <is>
-          <t>시공상 유의사항</t>
-        </is>
-      </c>
-      <c r="B76" s="4" t="n"/>
-      <c r="C76" s="4" t="n"/>
-      <c r="D76" s="4" t="n"/>
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>금지</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>사유</t>
+        </is>
+      </c>
     </row>
     <row r="77">
-      <c r="A77" s="5" t="inlineStr">
-        <is>
-          <t>항목</t>
-        </is>
-      </c>
-      <c r="B77" s="5" t="inlineStr">
-        <is>
-          <t>내용</t>
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>기존 천장 철거</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>원상복구 조건 위반 — M 시리즈 전제</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>슬래브 비접촉이 전부</t>
+          <t>돌차음판을 유닛에 삽입</t>
         </is>
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>유닛 상면 마블이 슬래브에 닿으면 M1의 근거가 사라진다. 새 공동 200mm 이상을 확보하고 상면 마블 두께를 그 안에서 정한다.</t>
+          <t>자중 25.5kg/㎡ · @450 필요 · 벽 하단 3.7kPa — 기존 천장 부착이 우선</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>벽 상단 턱 재료</t>
+          <t>돌차음판 · 유닛 상면 접촉</t>
         </is>
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>천장 하중 약 145kg이 좁은 지압면에 집중된다. 턱이 PB면 국부 압괴 우려가 있으므로 각재로 보강한다.</t>
+          <t>가운데 판과 유닛 연결 — 삼중 리프 분리 효과 상실</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>벽 하단 하중 검토</t>
+          <t>돌차음판 2T 대체</t>
         </is>
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>천장 145kg + 벽 920kg = 약 1,065kg, 접지 1.8㎡ 기준 5.8kPa로 AC-F-M2 방진층 설계 하중을 넘는다. 분산판 적용 시 약 3.5kPa. 마블 압축영구변형 데이터 미확보 상태이므로 벽 라인 고밀도 보강을 병행한다.</t>
+          <t>질량 1.8배 차이 — 4T 표준</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>스팬 한계 — M2는 @450 표준</t>
+          <t>벽지 위 무확인 부착</t>
         </is>
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>자중 25.5kg/㎡ 기준 @600은 2.4m, @450은 2.7m가 한계다. 아파트 방 폭이 대개 3m 안팎이므로 @450을 표준으로 잡는다.</t>
+          <t>벽지 박리 · 돌차음판 처짐</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>돌차음판 위치</t>
+          <t>기존 달대 하중 미검토</t>
         </is>
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>PB 아래 · 마블 위에 삽입한다. 실내 쪽에 질량을 두어야 삼중 리프 질량 분리 방향과 맞는다. PB 위에 붙이면 상면 마블과 붙어 분리 효과가 줄어든다.</t>
+          <t>약 두 배 하중 — 이탈 위험</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>벽-천장 접합은 강결</t>
+          <t>슬래브 타공 · 행거 병용</t>
         </is>
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>M1은 6면을 하나의 계로 묶는 것이 목적이므로 턱 위 방진 패드를 두지 않는다. 실 내부 상호 전달은 손실이 아니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="6" t="inlineStr">
-        <is>
-          <t>마감 그림자 홈</t>
-        </is>
-      </c>
-      <c r="B84" s="6" t="inlineStr">
-        <is>
-          <t>유닛은 시간이 지나면 반드시 처진다. 텍스를 벽 마감면에 밀착시키면 그 자리가 갈라지므로 5~10mm 홈을 둔다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="6" t="inlineStr">
-        <is>
-          <t>성능 범위 고지</t>
-        </is>
-      </c>
-      <c r="B85" s="6" t="inlineStr">
-        <is>
-          <t>위층 뛰는 소리와 저역은 대응하지 않는다. 기존 천장 존치 조건에서 구조적으로 불가능함을 계약 전 서면 고지한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="3" t="inlineStr">
-        <is>
-          <t>금지사항</t>
-        </is>
-      </c>
-      <c r="B87" s="4" t="n"/>
-      <c r="C87" s="4" t="n"/>
-      <c r="D87" s="4" t="n"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="5" t="inlineStr">
-        <is>
-          <t>금지</t>
-        </is>
-      </c>
-      <c r="B88" s="5" t="inlineStr">
-        <is>
-          <t>사유</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="6" t="inlineStr">
-        <is>
-          <t>기존 천장 철거</t>
-        </is>
-      </c>
-      <c r="B89" s="6" t="inlineStr">
-        <is>
-          <t>원상복구 조건 위반 — M 시리즈 전제</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="6" t="inlineStr">
-        <is>
-          <t>슬래브 타공 · 행거 병용</t>
-        </is>
-      </c>
-      <c r="B90" s="6" t="inlineStr">
-        <is>
-          <t>접촉점 0 원칙 위반 — M1 근거 상실</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="6" t="inlineStr">
-        <is>
-          <t>유닛 상면 슬래브 접촉</t>
-        </is>
-      </c>
-      <c r="B91" s="6" t="inlineStr">
-        <is>
-          <t>새 공동 소멸 · 강결 경로 발생</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="6" t="inlineStr">
-        <is>
-          <t>유닛 상면 마블 생략</t>
-        </is>
-      </c>
-      <c r="B92" s="6" t="inlineStr">
-        <is>
-          <t>공동 공진 — 표준 포함 항목</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="6" t="inlineStr">
-        <is>
-          <t>돌차음판 2T 대체</t>
-        </is>
-      </c>
-      <c r="B93" s="6" t="inlineStr">
-        <is>
-          <t>질량 1.8배 차이 — 4T 표준</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="6" t="inlineStr">
-        <is>
-          <t>차음석고 12.5T 대체</t>
-        </is>
-      </c>
-      <c r="B94" s="6" t="inlineStr">
-        <is>
-          <t>1장 20kg 초과 · 천장 시공 2인 필요</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="6" t="inlineStr">
-        <is>
-          <t>흡음텍스에 하중 부담</t>
-        </is>
-      </c>
-      <c r="B95" s="6" t="inlineStr">
-        <is>
-          <t>마감재 — 구조 지지 불가</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="6" t="inlineStr">
-        <is>
-          <t>벽 하단 분산판 생략</t>
-        </is>
-      </c>
-      <c r="B96" s="6" t="inlineStr">
-        <is>
-          <t>5.8kPa — 방진층 설계 하중 초과</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="6" t="inlineStr">
-        <is>
-          <t>스팬 3.0m @600 강행</t>
-        </is>
-      </c>
-      <c r="B97" s="6" t="inlineStr">
-        <is>
-          <t>처짐 15mm — 이격 잠식</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="6" t="inlineStr">
-        <is>
-          <t>위층 충격음 대응 목적 판매</t>
-        </is>
-      </c>
-      <c r="B98" s="6" t="inlineStr">
-        <is>
-          <t>삼중 리프 · 약 100Hz 딥 잔존</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="6" t="inlineStr">
-        <is>
-          <t>PB · MDF 마감판 추가</t>
-        </is>
-      </c>
-      <c r="B99" s="6" t="inlineStr">
-        <is>
-          <t>면밀도 절반 · 판 공진 · 가연재</t>
+          <t>접촉점 0 원칙 위반</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="A38:D38"/>
-    <mergeCell ref="A42:D42"/>
-    <mergeCell ref="A46:D46"/>
-    <mergeCell ref="A36:D36"/>
-    <mergeCell ref="A44:D44"/>
+  <mergeCells count="5">
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A33:D33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2689,7 +2519,7 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>L 시리즈 벽 · 천장 통일 검토 중. 폴리에스터 흡음단열재(KS F 5660) 50T 40K와 미네랄울 48K의 저역(125 · 250Hz) 흡음률 비교 데이터 확보 후 확정</t>
+          <t>L 시리즈 벽 · 천장 통일 검토 중. 폴리에스터 흡음단열재(KS F 5660) 50T 40K와 미네랄울 50K의 저역(125 · 250Hz) 흡음률 비교 데이터 확보 후 확정</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr"/>
